--- a/data/庫存明細.xlsx
+++ b/data/庫存明細.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,6 +485,866 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-M</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>杏色M</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>250</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-XL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>杏色XL</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>250</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>50</v>
+      </c>
+      <c r="K3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-M</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>深藍M</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>250</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>50</v>
+      </c>
+      <c r="K4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-XL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>深藍XL</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>250</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>50</v>
+      </c>
+      <c r="K5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HFA01020</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HFA01020-BGBK-F</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>翻領插肩袖寬鬆中長版短袖T恤</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>杏拼黑F</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>550</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>110</v>
+      </c>
+      <c r="K6" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-L</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>條紋L</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>600</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>120</v>
+      </c>
+      <c r="K7" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-M</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>條紋M</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>600</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>120</v>
+      </c>
+      <c r="K8" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-XL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>條紋XL</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>600</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>120</v>
+      </c>
+      <c r="K9" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HFA01022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HFA01022-BU-F</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>美式復古渡假風純棉短袖T恤</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>深海藍F</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>80</v>
+      </c>
+      <c r="K10" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HFA01022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HFA01022-WH-F</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>美式復古渡假風純棉短袖T恤</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>白色F</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>80</v>
+      </c>
+      <c r="K11" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HGI03022</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HGI03022-PK</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>新款PU皮立式化妝刷具旅行收納包</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>霧玫瑰</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" t="n">
+        <v>100</v>
+      </c>
+      <c r="K12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HGI03022</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HGI03022-WH</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>新款PU皮立式化妝刷具旅行收納包</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>白蛋色</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" t="n">
+        <v>100</v>
+      </c>
+      <c r="K13" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HGI03023-BK</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>100</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HGI03023-GY</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>奶霧灰</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>100</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" t="n">
+        <v>10</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HGI03023-WH</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>燕麥白</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>100</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HGI03024-100L</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>特大100L</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" t="n">
+        <v>280</v>
+      </c>
+      <c r="K17" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HGI03024-24L</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>小號24L</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J18" t="n">
+        <v>150</v>
+      </c>
+      <c r="K18" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HGI03024-40L</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>中號40L</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>10</v>
+      </c>
+      <c r="J19" t="n">
+        <v>180</v>
+      </c>
+      <c r="K19" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HGI03024-55L</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>大號55L</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>10</v>
+      </c>
+      <c r="J20" t="n">
+        <v>200</v>
+      </c>
+      <c r="K20" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HGI03024-66L</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>加大66L</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" t="n">
+        <v>250</v>
+      </c>
+      <c r="K21" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/庫存明細.xlsx
+++ b/data/庫存明細.xlsx
@@ -513,13 +513,13 @@
         <v>250</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
         <v>50</v>
@@ -556,13 +556,13 @@
         <v>250</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
         <v>50</v>
@@ -599,13 +599,13 @@
         <v>250</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>50</v>
@@ -728,13 +728,13 @@
         <v>600</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
         <v>120</v>
@@ -771,13 +771,13 @@
         <v>600</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="J8" t="n">
         <v>120</v>
@@ -900,13 +900,13 @@
         <v>400</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="J11" t="n">
         <v>80</v>
@@ -1115,13 +1115,13 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
         <v>10</v>
@@ -1158,13 +1158,13 @@
         <v>2800</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
         <v>280</v>
@@ -1201,13 +1201,13 @@
         <v>1500</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="I18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J18" t="n">
         <v>150</v>
@@ -1287,13 +1287,13 @@
         <v>2000</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="I20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
         <v>200</v>

--- a/data/庫存明細.xlsx
+++ b/data/庫存明細.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,6 +485,866 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-M</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>杏色M</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>250</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>650</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-XL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>杏色XL</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>250</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="n">
+        <v>650</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>50</v>
+      </c>
+      <c r="K3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-M</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>深藍M</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>250</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>195</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>50</v>
+      </c>
+      <c r="K4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-XL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>深藍XL</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>250</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>67</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>50</v>
+      </c>
+      <c r="K5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HFA01020</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HFA01020-BGBK-F</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>翻領插肩袖寬鬆中長版短袖T恤</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>杏拼黑F</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>550</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>110</v>
+      </c>
+      <c r="K6" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-L</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>條紋L</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>600</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>120</v>
+      </c>
+      <c r="K7" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-M</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>條紋M</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>600</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>120</v>
+      </c>
+      <c r="K8" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-XL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>條紋XL</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>600</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>120</v>
+      </c>
+      <c r="K9" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HFA01022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HFA01022-BU-F</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>美式復古渡假風純棉短袖T恤</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>深海藍F</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>80</v>
+      </c>
+      <c r="K10" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HFA01022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HFA01022-WH-F</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>美式復古渡假風純棉短袖T恤</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>白色F</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>80</v>
+      </c>
+      <c r="K11" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HGI03022</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HGI03022-PK</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>新款PU皮立式化妝刷具旅行收納包</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>霧玫瑰</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" t="n">
+        <v>100</v>
+      </c>
+      <c r="K12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HGI03022</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HGI03022-WH</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>新款PU皮立式化妝刷具旅行收納包</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>白蛋色</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>42</v>
+      </c>
+      <c r="I13" t="n">
+        <v>9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>100</v>
+      </c>
+      <c r="K13" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HGI03023-BK</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>100</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>75</v>
+      </c>
+      <c r="I14" t="n">
+        <v>9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HGI03023-GY</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>奶霧灰</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>100</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>135</v>
+      </c>
+      <c r="I15" t="n">
+        <v>9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>10</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HGI03023-WH</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>燕麥白</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>100</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>135</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HGI03024-100L</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>特大100L</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" t="n">
+        <v>280</v>
+      </c>
+      <c r="K17" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HGI03024-24L</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>小號24L</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>155</v>
+      </c>
+      <c r="I18" t="n">
+        <v>9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>150</v>
+      </c>
+      <c r="K18" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HGI03024-40L</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>中號40L</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>67</v>
+      </c>
+      <c r="I19" t="n">
+        <v>9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>180</v>
+      </c>
+      <c r="K19" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HGI03024-55L</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>大號55L</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>155</v>
+      </c>
+      <c r="I20" t="n">
+        <v>9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>200</v>
+      </c>
+      <c r="K20" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HGI03024-66L</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>加大66L</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>67</v>
+      </c>
+      <c r="I21" t="n">
+        <v>9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>250</v>
+      </c>
+      <c r="K21" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/庫存明細.xlsx
+++ b/data/庫存明細.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,13 +476,808 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>平均成本(庫存明細)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>平均成本(入庫)</t>
-        </is>
+          <t>平均成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-M</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>杏色M</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>250</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>155</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-XL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>杏色XL</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>250</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="n">
+        <v>872</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-M</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>深藍M</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>250</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>67</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-XL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>深藍XL</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>250</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>42</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HFA01020</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HFA01020-BGBK-F</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>翻領插肩袖寬鬆中長版短袖T恤</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>杏拼黑F</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>550</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-L</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>條紋L</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>600</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-M</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>條紋M</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>600</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-XL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>條紋XL</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>600</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HFA01022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HFA01022-BU-F</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>美式復古渡假風純棉短袖T恤</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>深海藍F</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HFA01022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HFA01022-WH-F</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>美式復古渡假風純棉短袖T恤</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>白色F</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HGI03022</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HGI03022-PK</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>新款PU皮立式化妝刷具旅行收納包</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>霧玫瑰</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HGI03022</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HGI03022-WH</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>新款PU皮立式化妝刷具旅行收納包</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>白蛋色</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HGI03023-BK</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>100</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>75</v>
+      </c>
+      <c r="I14" t="n">
+        <v>9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HGI03023-GY</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>奶霧灰</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>100</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HGI03023-WH</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>燕麥白</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>100</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>135</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HGI03024-100L</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>特大100L</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HGI03024-24L</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>小號24L</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J18" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HGI03024-40L</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>中號40L</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>10</v>
+      </c>
+      <c r="J19" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HGI03024-55L</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>大號55L</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>10</v>
+      </c>
+      <c r="J20" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HGI03024-66L</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>加大66L</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" t="n">
+        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/data/庫存明細.xlsx
+++ b/data/庫存明細.xlsx
@@ -11148,13 +11148,13 @@
         <v>7353.2139281044</v>
       </c>
       <c r="G268" t="n">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="H268" t="n">
-        <v>6427.01</v>
+        <v>9677.01</v>
       </c>
       <c r="I268" t="n">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="J268" t="n">
         <v>32</v>

--- a/data/庫存明細.xlsx
+++ b/data/庫存明細.xlsx
@@ -22022,10 +22022,10 @@
         </is>
       </c>
       <c r="E540" t="n">
-        <v>29</v>
+        <v>221</v>
       </c>
       <c r="F540" t="n">
-        <v>2610</v>
+        <v>19890</v>
       </c>
       <c r="G540" t="n">
         <v>88</v>
@@ -22034,7 +22034,7 @@
         <v>14973.08</v>
       </c>
       <c r="I540" t="n">
-        <v>-59</v>
+        <v>133</v>
       </c>
       <c r="J540" t="n">
         <v>90</v>
@@ -22062,10 +22062,10 @@
         </is>
       </c>
       <c r="E541" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F541" t="n">
-        <v>2160</v>
+        <v>3150</v>
       </c>
       <c r="G541" t="n">
         <v>23</v>
@@ -22074,7 +22074,7 @@
         <v>3973</v>
       </c>
       <c r="I541" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J541" t="n">
         <v>90</v>
@@ -22102,10 +22102,10 @@
         </is>
       </c>
       <c r="E542" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="F542" t="n">
-        <v>1440</v>
+        <v>4680</v>
       </c>
       <c r="G542" t="n">
         <v>19</v>
@@ -22114,7 +22114,7 @@
         <v>3266</v>
       </c>
       <c r="I542" t="n">
-        <v>-3</v>
+        <v>33</v>
       </c>
       <c r="J542" t="n">
         <v>90</v>
@@ -22142,10 +22142,10 @@
         </is>
       </c>
       <c r="E543" t="n">
-        <v>38</v>
+        <v>182</v>
       </c>
       <c r="F543" t="n">
-        <v>3420</v>
+        <v>16380</v>
       </c>
       <c r="G543" t="n">
         <v>37</v>
@@ -22154,7 +22154,7 @@
         <v>6377.99</v>
       </c>
       <c r="I543" t="n">
-        <v>1</v>
+        <v>145</v>
       </c>
       <c r="J543" t="n">
         <v>90</v>
@@ -22182,10 +22182,10 @@
         </is>
       </c>
       <c r="E544" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F544" t="n">
-        <v>2340</v>
+        <v>4500</v>
       </c>
       <c r="G544" t="n">
         <v>10</v>
@@ -22194,7 +22194,7 @@
         <v>1718</v>
       </c>
       <c r="I544" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J544" t="n">
         <v>90</v>
@@ -22222,10 +22222,10 @@
         </is>
       </c>
       <c r="E545" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="F545" t="n">
-        <v>990</v>
+        <v>4230</v>
       </c>
       <c r="G545" t="n">
         <v>10</v>
@@ -22234,7 +22234,7 @@
         <v>1718</v>
       </c>
       <c r="I545" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="J545" t="n">
         <v>90</v>

--- a/data/庫存明細.xlsx
+++ b/data/庫存明細.xlsx
@@ -17548,13 +17548,13 @@
         <v>24078.99576211669</v>
       </c>
       <c r="G428" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H428" t="n">
-        <v>16567.63</v>
+        <v>16768.63</v>
       </c>
       <c r="I428" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="J428" t="n">
         <v>32.6</v>
@@ -17628,13 +17628,13 @@
         <v>12178.24624523203</v>
       </c>
       <c r="G430" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H430" t="n">
-        <v>4906</v>
+        <v>5241</v>
       </c>
       <c r="I430" t="n">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="J430" t="n">
         <v>32</v>
@@ -17708,13 +17708,13 @@
         <v>4277.816291248312</v>
       </c>
       <c r="G432" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H432" t="n">
-        <v>2616.01</v>
+        <v>2817.01</v>
       </c>
       <c r="I432" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J432" t="n">
         <v>31.9</v>
@@ -18028,13 +18028,13 @@
         <v>15799.15461193239</v>
       </c>
       <c r="G440" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H440" t="n">
-        <v>6846.04</v>
+        <v>7047.04</v>
       </c>
       <c r="I440" t="n">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="J440" t="n">
         <v>32.2</v>
@@ -18188,13 +18188,13 @@
         <v>4214.391784136446</v>
       </c>
       <c r="G444" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H444" t="n">
-        <v>1451</v>
+        <v>1652</v>
       </c>
       <c r="I444" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="J444" t="n">
         <v>31.9</v>
@@ -18508,13 +18508,13 @@
         <v>4557.005135046255</v>
       </c>
       <c r="G452" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H452" t="n">
-        <v>3132</v>
+        <v>3333</v>
       </c>
       <c r="I452" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J452" t="n">
         <v>32.1</v>

--- a/data/庫存明細.xlsx
+++ b/data/庫存明細.xlsx
@@ -788,13 +788,13 @@
         <v>956.6557582186828</v>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H9" t="n">
-        <v>686</v>
+        <v>884</v>
       </c>
       <c r="I9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J9" t="n">
         <v>30.9</v>
@@ -1228,13 +1228,13 @@
         <v>2934.225694267281</v>
       </c>
       <c r="G20" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H20" t="n">
-        <v>2608</v>
+        <v>3134</v>
       </c>
       <c r="I20" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J20" t="n">
         <v>61.1</v>
@@ -1908,13 +1908,13 @@
         <v>2807.343018544294</v>
       </c>
       <c r="G37" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H37" t="n">
-        <v>4137</v>
+        <v>4488</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
         <v>61</v>
@@ -1948,13 +1948,13 @@
         <v>2379.682831839913</v>
       </c>
       <c r="G38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H38" t="n">
-        <v>1579</v>
+        <v>1754</v>
       </c>
       <c r="I38" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J38" t="n">
         <v>61</v>
@@ -2748,13 +2748,13 @@
         <v>3110.069541031239</v>
       </c>
       <c r="G58" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H58" t="n">
-        <v>2957</v>
+        <v>3311</v>
       </c>
       <c r="I58" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J58" t="n">
         <v>61</v>
@@ -2788,13 +2788,13 @@
         <v>2194.914936001593</v>
       </c>
       <c r="G59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H59" t="n">
-        <v>1225</v>
+        <v>1400</v>
       </c>
       <c r="I59" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J59" t="n">
         <v>61</v>
@@ -2828,13 +2828,13 @@
         <v>2993.349000500423</v>
       </c>
       <c r="G60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H60" t="n">
-        <v>2898.99</v>
+        <v>3073.99</v>
       </c>
       <c r="I60" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J60" t="n">
         <v>61.1</v>
@@ -4748,13 +4748,13 @@
         <v>639.2073602264686</v>
       </c>
       <c r="G108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H108" t="n">
-        <v>1495</v>
+        <v>1794</v>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J108" t="n">
         <v>106.5</v>
@@ -4828,13 +4828,13 @@
         <v>1437.120188993849</v>
       </c>
       <c r="G110" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H110" t="n">
-        <v>1190</v>
+        <v>1788</v>
       </c>
       <c r="I110" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J110" t="n">
         <v>110.5</v>
@@ -4948,13 +4948,13 @@
         <v>843.6103475795529</v>
       </c>
       <c r="G113" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H113" t="n">
-        <v>1495</v>
+        <v>1794</v>
       </c>
       <c r="I113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
         <v>105.5</v>
@@ -5108,13 +5108,13 @@
         <v>530.1051665696064</v>
       </c>
       <c r="G117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H117" t="n">
-        <v>299</v>
+        <v>598</v>
       </c>
       <c r="I117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J117" t="n">
         <v>132.5</v>
@@ -5308,13 +5308,13 @@
         <v>292.8145199761478</v>
       </c>
       <c r="G122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H122" t="n">
-        <v>388</v>
+        <v>776</v>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J122" t="n">
         <v>146.4</v>
@@ -7708,13 +7708,13 @@
         <v>69.66894676116696</v>
       </c>
       <c r="G182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H182" t="n">
-        <v>170</v>
+        <v>255</v>
       </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J182" t="n">
         <v>23.2</v>
@@ -7948,13 +7948,13 @@
         <v>8820.325021595992</v>
       </c>
       <c r="G188" t="n">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="H188" t="n">
-        <v>8747.030000000001</v>
+        <v>9362.030000000001</v>
       </c>
       <c r="I188" t="n">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="J188" t="n">
         <v>21.2</v>
@@ -7988,13 +7988,13 @@
         <v>6492.996560600062</v>
       </c>
       <c r="G189" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H189" t="n">
-        <v>5089</v>
+        <v>5378</v>
       </c>
       <c r="I189" t="n">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="J189" t="n">
         <v>21.4</v>
@@ -8028,13 +8028,13 @@
         <v>7093.134514171942</v>
       </c>
       <c r="G190" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="H190" t="n">
-        <v>7320.02</v>
+        <v>7660.02</v>
       </c>
       <c r="I190" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J190" t="n">
         <v>21.3</v>
@@ -8188,13 +8188,13 @@
         <v>3210.465841202406</v>
       </c>
       <c r="G194" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H194" t="n">
-        <v>4465.97</v>
+        <v>4561.97</v>
       </c>
       <c r="I194" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J194" t="n">
         <v>21.4</v>
@@ -8268,13 +8268,13 @@
         <v>2344.137022939894</v>
       </c>
       <c r="G196" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H196" t="n">
-        <v>1760</v>
+        <v>1808</v>
       </c>
       <c r="I196" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J196" t="n">
         <v>21.3</v>
@@ -8308,13 +8308,13 @@
         <v>3097.45104820309</v>
       </c>
       <c r="G197" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H197" t="n">
-        <v>2892.01</v>
+        <v>2941.01</v>
       </c>
       <c r="I197" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J197" t="n">
         <v>21.5</v>
@@ -8348,13 +8348,13 @@
         <v>2477.36136015391</v>
       </c>
       <c r="G198" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H198" t="n">
-        <v>959</v>
+        <v>1008</v>
       </c>
       <c r="I198" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J198" t="n">
         <v>21.5</v>
@@ -8388,13 +8388,13 @@
         <v>2431.472550272069</v>
       </c>
       <c r="G199" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H199" t="n">
-        <v>1111</v>
+        <v>1160</v>
       </c>
       <c r="I199" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J199" t="n">
         <v>21.3</v>
@@ -8428,13 +8428,13 @@
         <v>3614.708327005422</v>
       </c>
       <c r="G200" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H200" t="n">
-        <v>4794.01</v>
+        <v>4892.01</v>
       </c>
       <c r="I200" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J200" t="n">
         <v>21.5</v>
@@ -8468,13 +8468,13 @@
         <v>3100.324455986782</v>
       </c>
       <c r="G201" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H201" t="n">
-        <v>2242</v>
+        <v>2485</v>
       </c>
       <c r="I201" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J201" t="n">
         <v>21.8</v>
@@ -8508,13 +8508,13 @@
         <v>2426.259921387876</v>
       </c>
       <c r="G202" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H202" t="n">
-        <v>1634</v>
+        <v>1826</v>
       </c>
       <c r="I202" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J202" t="n">
         <v>21.5</v>
@@ -8548,13 +8548,13 @@
         <v>3473.1574360366</v>
       </c>
       <c r="G203" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H203" t="n">
-        <v>2598</v>
+        <v>2695</v>
       </c>
       <c r="I203" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J203" t="n">
         <v>21.6</v>
@@ -8628,13 +8628,13 @@
         <v>2377.172839501409</v>
       </c>
       <c r="G205" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H205" t="n">
-        <v>1859</v>
+        <v>1955</v>
       </c>
       <c r="I205" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J205" t="n">
         <v>21.4</v>
@@ -8668,13 +8668,13 @@
         <v>6858.783456591403</v>
       </c>
       <c r="G206" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H206" t="n">
-        <v>7219.97</v>
+        <v>7368.97</v>
       </c>
       <c r="I206" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J206" t="n">
         <v>38.8</v>
@@ -8708,13 +8708,13 @@
         <v>6138.892895197684</v>
       </c>
       <c r="G207" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H207" t="n">
-        <v>5403.03</v>
+        <v>5702.03</v>
       </c>
       <c r="I207" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="J207" t="n">
         <v>38.6</v>
@@ -8748,13 +8748,13 @@
         <v>5721.94231486415</v>
       </c>
       <c r="G208" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H208" t="n">
-        <v>3098</v>
+        <v>3765</v>
       </c>
       <c r="I208" t="n">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="J208" t="n">
         <v>38.7</v>
@@ -8788,13 +8788,13 @@
         <v>10574.52751657256</v>
       </c>
       <c r="G209" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H209" t="n">
-        <v>7081.01</v>
+        <v>7455.01</v>
       </c>
       <c r="I209" t="n">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="J209" t="n">
         <v>38.7</v>
@@ -8828,13 +8828,13 @@
         <v>9076.248924434469</v>
       </c>
       <c r="G210" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H210" t="n">
-        <v>5276</v>
+        <v>5648</v>
       </c>
       <c r="I210" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="J210" t="n">
         <v>38.6</v>
@@ -8868,13 +8868,13 @@
         <v>8845.542984293323</v>
       </c>
       <c r="G211" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H211" t="n">
-        <v>4266.01</v>
+        <v>4489.01</v>
       </c>
       <c r="I211" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J211" t="n">
         <v>38.6</v>
@@ -8908,13 +8908,13 @@
         <v>5817.964418999271</v>
       </c>
       <c r="G212" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="H212" t="n">
-        <v>4095</v>
+        <v>4619</v>
       </c>
       <c r="I212" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="J212" t="n">
         <v>38.8</v>
@@ -8948,13 +8948,13 @@
         <v>4497.376171268729</v>
       </c>
       <c r="G213" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H213" t="n">
-        <v>2918.98</v>
+        <v>3068.98</v>
       </c>
       <c r="I213" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J213" t="n">
         <v>39.1</v>
@@ -8988,13 +8988,13 @@
         <v>4884.410569052256</v>
       </c>
       <c r="G214" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H214" t="n">
-        <v>3581.01</v>
+        <v>3876.01</v>
       </c>
       <c r="I214" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="J214" t="n">
         <v>38.8</v>
@@ -9028,13 +9028,13 @@
         <v>6177.957882236397</v>
       </c>
       <c r="G215" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H215" t="n">
-        <v>4898.99</v>
+        <v>5195.99</v>
       </c>
       <c r="I215" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J215" t="n">
         <v>38.9</v>
@@ -9068,13 +9068,13 @@
         <v>5057.594358672195</v>
       </c>
       <c r="G216" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H216" t="n">
-        <v>4310.03</v>
+        <v>4459.03</v>
       </c>
       <c r="I216" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J216" t="n">
         <v>38.6</v>
@@ -9108,13 +9108,13 @@
         <v>5229.21327964221</v>
       </c>
       <c r="G217" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H217" t="n">
-        <v>3827</v>
+        <v>4201</v>
       </c>
       <c r="I217" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="J217" t="n">
         <v>38.7</v>
@@ -9148,13 +9148,13 @@
         <v>5983.230086064323</v>
       </c>
       <c r="G218" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H218" t="n">
-        <v>7483.01</v>
+        <v>7856.01</v>
       </c>
       <c r="I218" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="J218" t="n">
         <v>38.6</v>
@@ -9188,13 +9188,13 @@
         <v>5419.749743070107</v>
       </c>
       <c r="G219" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H219" t="n">
-        <v>5268</v>
+        <v>5718</v>
       </c>
       <c r="I219" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="J219" t="n">
         <v>38.4</v>
@@ -9228,13 +9228,13 @@
         <v>5390.032861960473</v>
       </c>
       <c r="G220" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="H220" t="n">
-        <v>3549.01</v>
+        <v>3996.01</v>
       </c>
       <c r="I220" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="J220" t="n">
         <v>38.5</v>
@@ -9268,13 +9268,13 @@
         <v>5281.904212347041</v>
       </c>
       <c r="G221" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H221" t="n">
-        <v>3736.02</v>
+        <v>3886.02</v>
       </c>
       <c r="I221" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J221" t="n">
         <v>38.8</v>
@@ -9348,13 +9348,13 @@
         <v>4359.557018842648</v>
       </c>
       <c r="G223" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H223" t="n">
-        <v>2229.01</v>
+        <v>2821.01</v>
       </c>
       <c r="I223" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J223" t="n">
         <v>38.9</v>
@@ -10708,13 +10708,13 @@
         <v>1214.906607383356</v>
       </c>
       <c r="G257" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H257" t="n">
-        <v>2071</v>
+        <v>2566</v>
       </c>
       <c r="I257" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J257" t="n">
         <v>41.9</v>
@@ -10788,13 +10788,13 @@
         <v>1005.43995093795</v>
       </c>
       <c r="G259" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H259" t="n">
-        <v>297</v>
+        <v>396</v>
       </c>
       <c r="I259" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J259" t="n">
         <v>41.9</v>
@@ -10868,13 +10868,13 @@
         <v>502.719975468975</v>
       </c>
       <c r="G261" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H261" t="n">
-        <v>691</v>
+        <v>889</v>
       </c>
       <c r="I261" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J261" t="n">
         <v>41.9</v>
@@ -10948,13 +10948,13 @@
         <v>460.8266441798938</v>
       </c>
       <c r="G263" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H263" t="n">
-        <v>786</v>
+        <v>885</v>
       </c>
       <c r="I263" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J263" t="n">
         <v>41.9</v>
@@ -11188,13 +11188,13 @@
         <v>2966.708216216216</v>
       </c>
       <c r="G269" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H269" t="n">
-        <v>1315</v>
+        <v>1511</v>
       </c>
       <c r="I269" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J269" t="n">
         <v>19</v>
@@ -11268,13 +11268,13 @@
         <v>2414.683322072072</v>
       </c>
       <c r="G271" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H271" t="n">
-        <v>484</v>
+        <v>680</v>
       </c>
       <c r="I271" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="J271" t="n">
         <v>19</v>
@@ -11308,13 +11308,13 @@
         <v>8835.476914523651</v>
       </c>
       <c r="G272" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="H272" t="n">
-        <v>5719.75</v>
+        <v>7491.75</v>
       </c>
       <c r="I272" t="n">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="J272" t="n">
         <v>41.9</v>
@@ -11348,13 +11348,13 @@
         <v>11871.21576684038</v>
       </c>
       <c r="G273" t="n">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="H273" t="n">
-        <v>13413.96</v>
+        <v>18111.96</v>
       </c>
       <c r="I273" t="n">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="J273" t="n">
         <v>43.3</v>
@@ -11388,13 +11388,13 @@
         <v>13752.52635780305</v>
       </c>
       <c r="G274" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="H274" t="n">
-        <v>9900.01</v>
+        <v>15107.01</v>
       </c>
       <c r="I274" t="n">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="J274" t="n">
         <v>76.40000000000001</v>
@@ -11428,13 +11428,13 @@
         <v>22190.3686775583</v>
       </c>
       <c r="G275" t="n">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="H275" t="n">
-        <v>11431</v>
+        <v>17988</v>
       </c>
       <c r="I275" t="n">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="J275" t="n">
         <v>100</v>
@@ -11468,13 +11468,13 @@
         <v>9874.011291767807</v>
       </c>
       <c r="G276" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="H276" t="n">
-        <v>6447.63</v>
+        <v>9407.629999999999</v>
       </c>
       <c r="I276" t="n">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="J276" t="n">
         <v>41.5</v>
@@ -11508,13 +11508,13 @@
         <v>10928.79625564627</v>
       </c>
       <c r="G277" t="n">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="H277" t="n">
-        <v>8471.690000000001</v>
+        <v>14142.69</v>
       </c>
       <c r="I277" t="n">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="J277" t="n">
         <v>44.2</v>
@@ -11548,13 +11548,13 @@
         <v>15853.258393118</v>
       </c>
       <c r="G278" t="n">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="H278" t="n">
-        <v>11668.95</v>
+        <v>17264.44</v>
       </c>
       <c r="I278" t="n">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="J278" t="n">
         <v>75.5</v>
@@ -11588,13 +11588,13 @@
         <v>21029.03083693337</v>
       </c>
       <c r="G279" t="n">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="H279" t="n">
-        <v>11473.3</v>
+        <v>17841.3</v>
       </c>
       <c r="I279" t="n">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="J279" t="n">
         <v>99.7</v>
@@ -11628,13 +11628,13 @@
         <v>5419.537422285545</v>
       </c>
       <c r="G280" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H280" t="n">
-        <v>2836</v>
+        <v>3055</v>
       </c>
       <c r="I280" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J280" t="n">
         <v>117.8</v>
@@ -11668,13 +11668,13 @@
         <v>7655.045302283541</v>
       </c>
       <c r="G281" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H281" t="n">
-        <v>2617</v>
+        <v>2856</v>
       </c>
       <c r="I281" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J281" t="n">
         <v>141.8</v>
@@ -11708,13 +11708,13 @@
         <v>6164.744376053452</v>
       </c>
       <c r="G282" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H282" t="n">
-        <v>3219</v>
+        <v>3657</v>
       </c>
       <c r="I282" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J282" t="n">
         <v>118.6</v>
@@ -11788,13 +11788,13 @@
         <v>7674.473892796754</v>
       </c>
       <c r="G284" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H284" t="n">
-        <v>3219</v>
+        <v>3657</v>
       </c>
       <c r="I284" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J284" t="n">
         <v>118.1</v>
@@ -11868,13 +11868,13 @@
         <v>1548.620555555555</v>
       </c>
       <c r="G286" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H286" t="n">
-        <v>1987</v>
+        <v>2344</v>
       </c>
       <c r="I286" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J286" t="n">
         <v>50</v>
@@ -11988,13 +11988,13 @@
         <v>6780.845161290315</v>
       </c>
       <c r="G289" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H289" t="n">
-        <v>2707</v>
+        <v>2826</v>
       </c>
       <c r="I289" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J289" t="n">
         <v>49.1</v>
@@ -12068,13 +12068,13 @@
         <v>6684.565564516128</v>
       </c>
       <c r="G291" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H291" t="n">
-        <v>2077</v>
+        <v>2152</v>
       </c>
       <c r="I291" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J291" t="n">
         <v>37.3</v>
@@ -12108,13 +12108,13 @@
         <v>5876.732473118279</v>
       </c>
       <c r="G292" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H292" t="n">
-        <v>4996</v>
+        <v>5109</v>
       </c>
       <c r="I292" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J292" t="n">
         <v>50.7</v>
@@ -12188,13 +12188,13 @@
         <v>6299.382526881719</v>
       </c>
       <c r="G294" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H294" t="n">
-        <v>3024</v>
+        <v>3253</v>
       </c>
       <c r="I294" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="J294" t="n">
         <v>37.3</v>
@@ -12508,13 +12508,13 @@
         <v>7544.350552313237</v>
       </c>
       <c r="G302" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H302" t="n">
-        <v>14134</v>
+        <v>18075</v>
       </c>
       <c r="I302" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J302" t="n">
         <v>150.9</v>
@@ -12588,13 +12588,13 @@
         <v>6931.823938796249</v>
       </c>
       <c r="G304" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H304" t="n">
-        <v>8672</v>
+        <v>10655</v>
       </c>
       <c r="I304" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J304" t="n">
         <v>150.7</v>
@@ -12668,13 +12668,13 @@
         <v>2264.81342338807</v>
       </c>
       <c r="G306" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H306" t="n">
-        <v>3156</v>
+        <v>3551</v>
       </c>
       <c r="I306" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J306" t="n">
         <v>151</v>
@@ -12708,13 +12708,13 @@
         <v>2424.383963612852</v>
       </c>
       <c r="G307" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H307" t="n">
-        <v>3566</v>
+        <v>3961</v>
       </c>
       <c r="I307" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J307" t="n">
         <v>151.5</v>
@@ -12748,13 +12748,13 @@
         <v>4077.551372506819</v>
       </c>
       <c r="G308" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H308" t="n">
-        <v>6320</v>
+        <v>7508</v>
       </c>
       <c r="I308" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J308" t="n">
         <v>151</v>
@@ -13268,13 +13268,13 @@
         <v>1782.05907533661</v>
       </c>
       <c r="G321" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H321" t="n">
-        <v>1556</v>
+        <v>1751</v>
       </c>
       <c r="I321" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J321" t="n">
         <v>84.90000000000001</v>
@@ -13308,13 +13308,13 @@
         <v>1966.702738770242</v>
       </c>
       <c r="G322" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H322" t="n">
-        <v>2539</v>
+        <v>2937</v>
       </c>
       <c r="I322" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J322" t="n">
         <v>85.5</v>
@@ -13348,13 +13348,13 @@
         <v>1783.531179255625</v>
       </c>
       <c r="G323" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H323" t="n">
-        <v>2147</v>
+        <v>2346</v>
       </c>
       <c r="I323" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J323" t="n">
         <v>84.90000000000001</v>
@@ -13388,13 +13388,13 @@
         <v>2383.757106406264</v>
       </c>
       <c r="G324" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H324" t="n">
-        <v>2764</v>
+        <v>3357</v>
       </c>
       <c r="I324" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J324" t="n">
         <v>85.09999999999999</v>
@@ -14028,13 +14028,13 @@
         <v>2679.95</v>
       </c>
       <c r="G340" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H340" t="n">
-        <v>1160</v>
+        <v>1459</v>
       </c>
       <c r="I340" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J340" t="n">
         <v>141</v>
@@ -14468,13 +14468,13 @@
         <v>370.5539293248945</v>
       </c>
       <c r="G351" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H351" t="n">
-        <v>159</v>
+        <v>318</v>
       </c>
       <c r="I351" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J351" t="n">
         <v>74.09999999999999</v>
@@ -14628,13 +14628,13 @@
         <v>357.7146404678766</v>
       </c>
       <c r="G355" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H355" t="n">
-        <v>702</v>
+        <v>820</v>
       </c>
       <c r="I355" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J355" t="n">
         <v>16.3</v>
@@ -14668,13 +14668,13 @@
         <v>299.4483556960607</v>
       </c>
       <c r="G356" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H356" t="n">
-        <v>761</v>
+        <v>997</v>
       </c>
       <c r="I356" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J356" t="n">
         <v>16.6</v>
@@ -14708,13 +14708,13 @@
         <v>299.4483556960607</v>
       </c>
       <c r="G357" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H357" t="n">
-        <v>762.99</v>
+        <v>998.99</v>
       </c>
       <c r="I357" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J357" t="n">
         <v>16.6</v>
@@ -14748,13 +14748,13 @@
         <v>332.7203952178452</v>
       </c>
       <c r="G358" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H358" t="n">
-        <v>997</v>
+        <v>1115</v>
       </c>
       <c r="I358" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J358" t="n">
         <v>16.6</v>
@@ -14788,13 +14788,13 @@
         <v>282.2995172833205</v>
       </c>
       <c r="G359" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H359" t="n">
-        <v>587</v>
+        <v>705</v>
       </c>
       <c r="I359" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J359" t="n">
         <v>16.6</v>
@@ -15508,13 +15508,13 @@
         <v>1174.61</v>
       </c>
       <c r="G377" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H377" t="n">
-        <v>1776</v>
+        <v>1875</v>
       </c>
       <c r="I377" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J377" t="n">
         <v>25.5</v>
@@ -16028,13 +16028,13 @@
         <v>131.8893045894158</v>
       </c>
       <c r="G390" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H390" t="n">
-        <v>233</v>
+        <v>272</v>
       </c>
       <c r="I390" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J390" t="n">
         <v>12</v>
@@ -16148,13 +16148,13 @@
         <v>105.7658385851448</v>
       </c>
       <c r="G393" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H393" t="n">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="I393" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J393" t="n">
         <v>8.1</v>
@@ -16228,13 +16228,13 @@
         <v>234.9983087291555</v>
       </c>
       <c r="G395" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H395" t="n">
-        <v>528</v>
+        <v>587</v>
       </c>
       <c r="I395" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J395" t="n">
         <v>16.8</v>
@@ -16268,13 +16268,13 @@
         <v>175.4517364428675</v>
       </c>
       <c r="G396" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H396" t="n">
-        <v>470</v>
+        <v>529</v>
       </c>
       <c r="I396" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J396" t="n">
         <v>16</v>
@@ -17548,13 +17548,13 @@
         <v>24078.99576211669</v>
       </c>
       <c r="G428" t="n">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="H428" t="n">
-        <v>16833.63</v>
+        <v>18003.63</v>
       </c>
       <c r="I428" t="n">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="J428" t="n">
         <v>32.6</v>
@@ -17588,13 +17588,13 @@
         <v>16869.51406691531</v>
       </c>
       <c r="G429" t="n">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="H429" t="n">
-        <v>11405.03</v>
+        <v>12765.03</v>
       </c>
       <c r="I429" t="n">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="J429" t="n">
         <v>32.4</v>
@@ -17628,13 +17628,13 @@
         <v>12178.24624523203</v>
       </c>
       <c r="G430" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H430" t="n">
-        <v>5241</v>
+        <v>5724</v>
       </c>
       <c r="I430" t="n">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="J430" t="n">
         <v>32</v>
@@ -17668,13 +17668,13 @@
         <v>24785.01784967303</v>
       </c>
       <c r="G431" t="n">
-        <v>287</v>
+        <v>334</v>
       </c>
       <c r="H431" t="n">
-        <v>18568.97</v>
+        <v>21696.97</v>
       </c>
       <c r="I431" t="n">
-        <v>473</v>
+        <v>426</v>
       </c>
       <c r="J431" t="n">
         <v>32.6</v>
@@ -17748,13 +17748,13 @@
         <v>3706.137813458587</v>
       </c>
       <c r="G433" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H433" t="n">
-        <v>1557.02</v>
+        <v>1681.02</v>
       </c>
       <c r="I433" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J433" t="n">
         <v>31.9</v>
@@ -17828,13 +17828,13 @@
         <v>4949.586645438143</v>
       </c>
       <c r="G435" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H435" t="n">
-        <v>3336.01</v>
+        <v>3464.01</v>
       </c>
       <c r="I435" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J435" t="n">
         <v>32.1</v>
@@ -17868,13 +17868,13 @@
         <v>16046.59840083953</v>
       </c>
       <c r="G436" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H436" t="n">
-        <v>5511.01</v>
+        <v>5918.01</v>
       </c>
       <c r="I436" t="n">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="J436" t="n">
         <v>32.2</v>
@@ -17908,13 +17908,13 @@
         <v>13840.00100760856</v>
       </c>
       <c r="G437" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H437" t="n">
-        <v>4111.02</v>
+        <v>4591.02</v>
       </c>
       <c r="I437" t="n">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="J437" t="n">
         <v>32</v>
@@ -17948,13 +17948,13 @@
         <v>12793.90481043237</v>
       </c>
       <c r="G438" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H438" t="n">
-        <v>1576.01</v>
+        <v>1762.01</v>
       </c>
       <c r="I438" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="J438" t="n">
         <v>32.1</v>
@@ -17988,13 +17988,13 @@
         <v>17205.95998762394</v>
       </c>
       <c r="G439" t="n">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="H439" t="n">
-        <v>10386.03</v>
+        <v>11805.03</v>
       </c>
       <c r="I439" t="n">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="J439" t="n">
         <v>32.2</v>
@@ -18028,13 +18028,13 @@
         <v>15799.15461193239</v>
       </c>
       <c r="G440" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="H440" t="n">
-        <v>7112.04</v>
+        <v>7581.04</v>
       </c>
       <c r="I440" t="n">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="J440" t="n">
         <v>32.2</v>
@@ -18068,13 +18068,13 @@
         <v>14499.96302839446</v>
       </c>
       <c r="G441" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H441" t="n">
-        <v>4763.04</v>
+        <v>5177.04</v>
       </c>
       <c r="I441" t="n">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="J441" t="n">
         <v>32.2</v>
@@ -18108,13 +18108,13 @@
         <v>11773.6131440446</v>
       </c>
       <c r="G442" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H442" t="n">
-        <v>1784</v>
+        <v>2039</v>
       </c>
       <c r="I442" t="n">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="J442" t="n">
         <v>32.1</v>
@@ -18148,13 +18148,13 @@
         <v>17690.10399857966</v>
       </c>
       <c r="G443" t="n">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="H443" t="n">
-        <v>10989.06</v>
+        <v>12674.06</v>
       </c>
       <c r="I443" t="n">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="J443" t="n">
         <v>32.2</v>
@@ -18308,13 +18308,13 @@
         <v>4665.981427363285</v>
       </c>
       <c r="G447" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H447" t="n">
-        <v>1845</v>
+        <v>1980</v>
       </c>
       <c r="I447" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J447" t="n">
         <v>32</v>
@@ -18348,13 +18348,13 @@
         <v>3907.309711275011</v>
       </c>
       <c r="G448" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H448" t="n">
-        <v>1263</v>
+        <v>1398</v>
       </c>
       <c r="I448" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J448" t="n">
         <v>31.8</v>
@@ -18388,13 +18388,13 @@
         <v>3830.433362978586</v>
       </c>
       <c r="G449" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H449" t="n">
-        <v>966.01</v>
+        <v>1035.01</v>
       </c>
       <c r="I449" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J449" t="n">
         <v>31.9</v>
@@ -18468,13 +18468,13 @@
         <v>4472.896439427174</v>
       </c>
       <c r="G451" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H451" t="n">
-        <v>2091</v>
+        <v>2364</v>
       </c>
       <c r="I451" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="J451" t="n">
         <v>31.9</v>
@@ -18548,13 +18548,13 @@
         <v>4118.102010244032</v>
       </c>
       <c r="G453" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H453" t="n">
-        <v>2604.02</v>
+        <v>2673.02</v>
       </c>
       <c r="I453" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J453" t="n">
         <v>31.9</v>
@@ -18588,13 +18588,13 @@
         <v>5703.088314199615</v>
       </c>
       <c r="G454" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H454" t="n">
-        <v>7178.98</v>
+        <v>7451.98</v>
       </c>
       <c r="I454" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="J454" t="n">
         <v>32.2</v>
@@ -18788,13 +18788,13 @@
         <v>8153.778558395213</v>
       </c>
       <c r="G459" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H459" t="n">
-        <v>5699.02</v>
+        <v>6011.02</v>
       </c>
       <c r="I459" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J459" t="n">
         <v>46.3</v>
@@ -18828,13 +18828,13 @@
         <v>4986.25616575122</v>
       </c>
       <c r="G460" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H460" t="n">
-        <v>3672</v>
+        <v>3751</v>
       </c>
       <c r="I460" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J460" t="n">
         <v>45.7</v>
@@ -18908,13 +18908,13 @@
         <v>7622.765321555606</v>
       </c>
       <c r="G462" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="H462" t="n">
-        <v>6890.02</v>
+        <v>7727.02</v>
       </c>
       <c r="I462" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="J462" t="n">
         <v>46.2</v>
@@ -18948,13 +18948,13 @@
         <v>4805.713020014261</v>
       </c>
       <c r="G463" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H463" t="n">
-        <v>2856.01</v>
+        <v>3480.01</v>
       </c>
       <c r="I463" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="J463" t="n">
         <v>45.8</v>
@@ -18988,13 +18988,13 @@
         <v>3922.482028063892</v>
       </c>
       <c r="G464" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H464" t="n">
-        <v>3578</v>
+        <v>3736</v>
       </c>
       <c r="I464" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J464" t="n">
         <v>45.6</v>
@@ -19068,13 +19068,13 @@
         <v>6903.090458708815</v>
       </c>
       <c r="G466" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H466" t="n">
-        <v>4962</v>
+        <v>5716</v>
       </c>
       <c r="I466" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J466" t="n">
         <v>45.7</v>
@@ -19148,13 +19148,13 @@
         <v>4630.757291191487</v>
       </c>
       <c r="G468" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H468" t="n">
-        <v>1291</v>
+        <v>1370</v>
       </c>
       <c r="I468" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J468" t="n">
         <v>45.4</v>
@@ -19228,13 +19228,13 @@
         <v>5273.266749358148</v>
       </c>
       <c r="G470" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H470" t="n">
-        <v>2866.02</v>
+        <v>3020.02</v>
       </c>
       <c r="I470" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J470" t="n">
         <v>45.5</v>
@@ -19268,13 +19268,13 @@
         <v>4920.918465458753</v>
       </c>
       <c r="G471" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H471" t="n">
-        <v>2073</v>
+        <v>2231</v>
       </c>
       <c r="I471" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J471" t="n">
         <v>45.6</v>
@@ -19308,13 +19308,13 @@
         <v>4373.160962987658</v>
       </c>
       <c r="G472" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H472" t="n">
-        <v>2706</v>
+        <v>2785</v>
       </c>
       <c r="I472" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J472" t="n">
         <v>46</v>
@@ -19388,13 +19388,13 @@
         <v>5782.305124423918</v>
       </c>
       <c r="G474" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H474" t="n">
-        <v>2617.01</v>
+        <v>2696.01</v>
       </c>
       <c r="I474" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J474" t="n">
         <v>45.5</v>
@@ -19428,13 +19428,13 @@
         <v>5229.000183046368</v>
       </c>
       <c r="G475" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H475" t="n">
-        <v>2279.01</v>
+        <v>2512.01</v>
       </c>
       <c r="I475" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="J475" t="n">
         <v>45.5</v>
@@ -19468,13 +19468,13 @@
         <v>4493.825798892017</v>
       </c>
       <c r="G476" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H476" t="n">
-        <v>1656</v>
+        <v>1814</v>
       </c>
       <c r="I476" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J476" t="n">
         <v>45.4</v>
@@ -19548,13 +19548,13 @@
         <v>4954.985045868424</v>
       </c>
       <c r="G478" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H478" t="n">
-        <v>2085</v>
+        <v>2618</v>
       </c>
       <c r="I478" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="J478" t="n">
         <v>45.5</v>
@@ -19588,13 +19588,13 @@
         <v>4840.902931282813</v>
       </c>
       <c r="G479" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H479" t="n">
-        <v>2947</v>
+        <v>3338</v>
       </c>
       <c r="I479" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="J479" t="n">
         <v>45.7</v>
@@ -19668,13 +19668,13 @@
         <v>5435.496804877579</v>
       </c>
       <c r="G481" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H481" t="n">
-        <v>1319</v>
+        <v>1556</v>
       </c>
       <c r="I481" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="J481" t="n">
         <v>45.3</v>
@@ -19708,13 +19708,13 @@
         <v>5126.255300513635</v>
       </c>
       <c r="G482" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H482" t="n">
-        <v>2919.01</v>
+        <v>3377.01</v>
       </c>
       <c r="I482" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J482" t="n">
         <v>45.4</v>
@@ -19748,13 +19748,13 @@
         <v>5274.17529942786</v>
       </c>
       <c r="G483" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H483" t="n">
-        <v>1275</v>
+        <v>1429</v>
       </c>
       <c r="I483" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J483" t="n">
         <v>45.5</v>
@@ -19788,13 +19788,13 @@
         <v>5464.591685500733</v>
       </c>
       <c r="G484" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H484" t="n">
-        <v>1600</v>
+        <v>1679</v>
       </c>
       <c r="I484" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J484" t="n">
         <v>45.2</v>
@@ -19828,13 +19828,13 @@
         <v>5119.747697402177</v>
       </c>
       <c r="G485" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H485" t="n">
-        <v>537</v>
+        <v>616</v>
       </c>
       <c r="I485" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J485" t="n">
         <v>45.3</v>
@@ -19908,13 +19908,13 @@
         <v>4311.570493890107</v>
       </c>
       <c r="G487" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H487" t="n">
-        <v>1741</v>
+        <v>1820</v>
       </c>
       <c r="I487" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J487" t="n">
         <v>45.4</v>
@@ -19988,13 +19988,13 @@
         <v>4471.92507862512</v>
       </c>
       <c r="G489" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H489" t="n">
-        <v>766</v>
+        <v>845</v>
       </c>
       <c r="I489" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J489" t="n">
         <v>45.2</v>
@@ -20028,13 +20028,13 @@
         <v>4447.311966320427</v>
       </c>
       <c r="G490" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H490" t="n">
-        <v>1778</v>
+        <v>1857</v>
       </c>
       <c r="I490" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J490" t="n">
         <v>45.4</v>
@@ -20588,13 +20588,13 @@
         <v>1022.222259584907</v>
       </c>
       <c r="G504" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H504" t="n">
-        <v>1333</v>
+        <v>1729</v>
       </c>
       <c r="I504" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J504" t="n">
         <v>46.5</v>
@@ -21588,13 +21588,13 @@
         <v>8545.890025842629</v>
       </c>
       <c r="G529" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H529" t="n">
-        <v>5894</v>
+        <v>6289</v>
       </c>
       <c r="I529" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J529" t="n">
         <v>170.9</v>
@@ -21708,13 +21708,13 @@
         <v>2892.294969478409</v>
       </c>
       <c r="G532" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H532" t="n">
-        <v>2744</v>
+        <v>3143</v>
       </c>
       <c r="I532" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J532" t="n">
         <v>170.1</v>
@@ -22028,13 +22028,13 @@
         <v>19890</v>
       </c>
       <c r="G540" t="n">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="H540" t="n">
-        <v>14973.08</v>
+        <v>22615.08</v>
       </c>
       <c r="I540" t="n">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="J540" t="n">
         <v>90</v>
@@ -22068,13 +22068,13 @@
         <v>3150</v>
       </c>
       <c r="G541" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H541" t="n">
-        <v>3973</v>
+        <v>4322</v>
       </c>
       <c r="I541" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J541" t="n">
         <v>90</v>
@@ -22148,13 +22148,13 @@
         <v>16380</v>
       </c>
       <c r="G543" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="H543" t="n">
-        <v>6377.99</v>
+        <v>11352.99</v>
       </c>
       <c r="I543" t="n">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="J543" t="n">
         <v>90</v>
@@ -22188,13 +22188,13 @@
         <v>4500</v>
       </c>
       <c r="G544" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H544" t="n">
-        <v>1718</v>
+        <v>2398</v>
       </c>
       <c r="I544" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J544" t="n">
         <v>90</v>
@@ -22228,13 +22228,13 @@
         <v>4230</v>
       </c>
       <c r="G545" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H545" t="n">
-        <v>1718</v>
+        <v>1888</v>
       </c>
       <c r="I545" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J545" t="n">
         <v>90</v>
@@ -22268,13 +22268,13 @@
         <v>299997</v>
       </c>
       <c r="G546" t="n">
-        <v>6402</v>
+        <v>11039</v>
       </c>
       <c r="H546" t="n">
-        <v>61484.64</v>
+        <v>106763.79</v>
       </c>
       <c r="I546" t="n">
-        <v>93597</v>
+        <v>88960</v>
       </c>
       <c r="J546" t="n">
         <v>3</v>
@@ -22308,13 +22308,13 @@
         <v>299997</v>
       </c>
       <c r="G547" t="n">
-        <v>1457</v>
+        <v>1640</v>
       </c>
       <c r="H547" t="n">
-        <v>14047.08</v>
+        <v>15840.08</v>
       </c>
       <c r="I547" t="n">
-        <v>98542</v>
+        <v>98359</v>
       </c>
       <c r="J547" t="n">
         <v>3</v>
@@ -22348,13 +22348,13 @@
         <v>299997</v>
       </c>
       <c r="G548" t="n">
-        <v>1103</v>
+        <v>1303</v>
       </c>
       <c r="H548" t="n">
-        <v>10631.56</v>
+        <v>12597.58</v>
       </c>
       <c r="I548" t="n">
-        <v>98896</v>
+        <v>98696</v>
       </c>
       <c r="J548" t="n">
         <v>3</v>
@@ -22388,13 +22388,13 @@
         <v>299997</v>
       </c>
       <c r="G549" t="n">
-        <v>3881</v>
+        <v>5308</v>
       </c>
       <c r="H549" t="n">
-        <v>37160.54</v>
+        <v>51150.79</v>
       </c>
       <c r="I549" t="n">
-        <v>96118</v>
+        <v>94691</v>
       </c>
       <c r="J549" t="n">
         <v>3</v>
@@ -22428,13 +22428,13 @@
         <v>299997</v>
       </c>
       <c r="G550" t="n">
-        <v>1139</v>
+        <v>1309</v>
       </c>
       <c r="H550" t="n">
-        <v>11004.38</v>
+        <v>12650.4</v>
       </c>
       <c r="I550" t="n">
-        <v>98860</v>
+        <v>98690</v>
       </c>
       <c r="J550" t="n">
         <v>3</v>
@@ -22468,13 +22468,13 @@
         <v>299997</v>
       </c>
       <c r="G551" t="n">
-        <v>792</v>
+        <v>940</v>
       </c>
       <c r="H551" t="n">
-        <v>7741.23</v>
+        <v>9218.23</v>
       </c>
       <c r="I551" t="n">
-        <v>99207</v>
+        <v>99059</v>
       </c>
       <c r="J551" t="n">
         <v>3</v>

--- a/data/庫存明細.xlsx
+++ b/data/庫存明細.xlsx
@@ -29428,13 +29428,13 @@
         <v>1095.582857142857</v>
       </c>
       <c r="G725" t="n">
-        <v>185</v>
+        <v>223</v>
       </c>
       <c r="H725" t="n">
-        <v>740</v>
+        <v>854</v>
       </c>
       <c r="I725" t="n">
-        <v>2182</v>
+        <v>2144</v>
       </c>
       <c r="J725" t="n">
         <v>0.5</v>
@@ -29508,13 +29508,13 @@
         <v>952.5599999999999</v>
       </c>
       <c r="G727" t="n">
-        <v>161</v>
+        <v>220</v>
       </c>
       <c r="H727" t="n">
-        <v>644</v>
+        <v>821</v>
       </c>
       <c r="I727" t="n">
-        <v>1897</v>
+        <v>1838</v>
       </c>
       <c r="J727" t="n">
         <v>0.5</v>
@@ -31628,13 +31628,13 @@
         <v>141424.0402855654</v>
       </c>
       <c r="G780" t="n">
-        <v>3590</v>
+        <v>3593</v>
       </c>
       <c r="H780" t="n">
-        <v>236031.53</v>
+        <v>236226.53</v>
       </c>
       <c r="I780" t="n">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="J780" t="n">
         <v>32</v>
@@ -31788,13 +31788,13 @@
         <v>152927.5378433798</v>
       </c>
       <c r="G784" t="n">
-        <v>4025</v>
+        <v>4028</v>
       </c>
       <c r="H784" t="n">
-        <v>263567.11</v>
+        <v>263762.11</v>
       </c>
       <c r="I784" t="n">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="J784" t="n">
         <v>32</v>
@@ -36788,13 +36788,13 @@
         <v>360.3927879777287</v>
       </c>
       <c r="G909" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H909" t="n">
-        <v>10.24</v>
+        <v>127.97</v>
       </c>
       <c r="I909" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="J909" t="n">
         <v>5.3</v>
